--- a/testcases/item-search/item-search-product-search.xlsx
+++ b/testcases/item-search/item-search-product-search.xlsx
@@ -243,7 +243,7 @@
     <t>No tooltip appears</t>
   </si>
   <si>
-    <t>TC-ISR-PRS-013</t>
+    <t>TC-ISR-PRS-007</t>
   </si>
   <si>
     <t>A barcode with no match shows the empty state</t>
@@ -270,7 +270,7 @@
     <t>The full set returns</t>
   </si>
   <si>
-    <t>TC-ISR-PRS-014</t>
+    <t>TC-ISR-PRS-008</t>
   </si>
   <si>
     <t>Sorting flips through the column menu</t>
@@ -297,7 +297,7 @@
     <t>The original order returns — rows with an empty Category cell first, then Audio</t>
   </si>
   <si>
-    <t>TC-ISR-PRS-015</t>
+    <t>TC-ISR-PRS-009</t>
   </si>
   <si>
     <t>Pagination moves between pages</t>
@@ -331,286 +331,286 @@
     <t>Page 1 returns with its original first row</t>
   </si>
   <si>
+    <t>TC-ISR-PRS-010</t>
+  </si>
+  <si>
+    <t>Rows-per-page offers five sizes</t>
+  </si>
+  <si>
+    <t>A default search has been executed</t>
+  </si>
+  <si>
+    <t>1. Read the rows-per-page control</t>
+  </si>
+  <si>
+    <t>It shows 50</t>
+  </si>
+  <si>
+    <t>2. Open it</t>
+  </si>
+  <si>
+    <t>Exactly five options are offered: 10, 20, 30, 40, 50</t>
+  </si>
+  <si>
+    <t>The list closes; 50 remains selected and the grid still shows 50 rows</t>
+  </si>
+  <si>
+    <t>TC-ISR-PRS-011</t>
+  </si>
+  <si>
+    <t>Grid Options hides and restores a column</t>
+  </si>
+  <si>
+    <t>A default search has been executed; all 13 columns visible</t>
+  </si>
+  <si>
+    <t>1. Click Grid Options</t>
+  </si>
+  <si>
+    <t>A menu opens with "Reset to Default View" and a Columns section listing 12 column entries, all checked; the Item column is not in the list</t>
+  </si>
+  <si>
+    <t>2. Click the Owned entry</t>
+  </si>
+  <si>
+    <t>The menu closes and the Owned column disappears from the grid</t>
+  </si>
+  <si>
+    <t>3. Open Grid Options again</t>
+  </si>
+  <si>
+    <t>The Owned entry now shows unchecked</t>
+  </si>
+  <si>
+    <t>4. Click Owned again</t>
+  </si>
+  <si>
+    <t>The Owned column returns to the grid</t>
+  </si>
+  <si>
+    <t>TC-ISR-PRS-012</t>
+  </si>
+  <si>
+    <t>An executed search survives leaving and returning</t>
+  </si>
+  <si>
+    <t>1. Type Amp into Any Field and click Search</t>
+  </si>
+  <si>
+    <t>Matching results load</t>
+  </si>
+  <si>
+    <t>2. note the count</t>
+  </si>
+  <si>
+    <t>The Any Field box still holds `Amp`, the same count shows, and the rows are back without clicking Search</t>
+  </si>
+  <si>
+    <t>3. Navigate away from the page entirely, then navigate back and wait for hydration</t>
+  </si>
+  <si>
+    <t>TC-ISR-PRS-013</t>
+  </si>
+  <si>
+    <t>The search panel collapses and expands</t>
+  </si>
+  <si>
+    <t>1. Click the collapse-search-panel button</t>
+  </si>
+  <si>
+    <t>The search panel hides and the grid area widens</t>
+  </si>
+  <si>
+    <t>2. Click the button again</t>
+  </si>
+  <si>
+    <t>The search panel returns with its values intact</t>
+  </si>
+  <si>
+    <t>TC-ISR-PRS-014</t>
+  </si>
+  <si>
+    <t>A numeric barcode returns the single product it is scanned under</t>
+  </si>
+  <si>
+    <t>The Products page is open with default criteria and no executed search</t>
+  </si>
+  <si>
+    <t>1. Type the barcode 5052320 into the barcode box</t>
+  </si>
+  <si>
+    <t>The box holds the value; the Any Field box stays empty</t>
+  </si>
+  <si>
+    <t>2. Click Search</t>
+  </si>
+  <si>
+    <t>The count reads one product found and the grid shows a single row</t>
+  </si>
+  <si>
+    <t>3. Read that row's Item and Product Code ID</t>
+  </si>
+  <si>
+    <t>Item "Allen &amp; Heath ZED24", Product Code ID 28592</t>
+  </si>
+  <si>
+    <t>TC-ISR-PRS-015</t>
+  </si>
+  <si>
+    <t>A barcode with letters resolves the same way as a numeric one</t>
+  </si>
+  <si>
+    <t>1. Type the barcode DFW0082529 into the barcode box</t>
+  </si>
+  <si>
+    <t>The box holds the value</t>
+  </si>
+  <si>
+    <t>One product found, a single row in the grid</t>
+  </si>
+  <si>
+    <t>Item "Shure ULXD1 Bodypack - G50", Product Code ID 71154</t>
+  </si>
+  <si>
     <t>TC-ISR-PRS-016</t>
   </si>
   <si>
-    <t>Rows-per-page offers five sizes</t>
-  </si>
-  <si>
-    <t>A default search has been executed</t>
-  </si>
-  <si>
-    <t>1. Read the rows-per-page control</t>
-  </si>
-  <si>
-    <t>It shows 50</t>
-  </si>
-  <si>
-    <t>2. Open it</t>
-  </si>
-  <si>
-    <t>Exactly five options are offered: 10, 20, 30, 40, 50</t>
-  </si>
-  <si>
-    <t>The list closes; 50 remains selected and the grid still shows 50 rows</t>
+    <t>Different barcodes on the same product all return that product</t>
+  </si>
+  <si>
+    <t>1. Search the barcode DFW0082529 and read the row's Product Code ID</t>
+  </si>
+  <si>
+    <t>One row, Product Code ID 71154</t>
+  </si>
+  <si>
+    <t>2. Replace the barcode with DFW0082517 and search again</t>
+  </si>
+  <si>
+    <t>One row, the same Product Code ID 71154</t>
+  </si>
+  <si>
+    <t>3. Replace the barcode with 5189939 and search again</t>
   </si>
   <si>
     <t>TC-ISR-PRS-017</t>
   </si>
   <si>
-    <t>Grid Options hides and restores a column</t>
-  </si>
-  <si>
-    <t>A default search has been executed; all 13 columns visible</t>
-  </si>
-  <si>
-    <t>1. Click Grid Options</t>
-  </si>
-  <si>
-    <t>A menu opens with "Reset to Default View" and a Columns section listing 12 column entries, all checked; the Item column is not in the list</t>
-  </si>
-  <si>
-    <t>2. Click the Owned entry</t>
-  </si>
-  <si>
-    <t>The menu closes and the Owned column disappears from the grid</t>
-  </si>
-  <si>
-    <t>3. Open Grid Options again</t>
-  </si>
-  <si>
-    <t>The Owned entry now shows unchecked</t>
-  </si>
-  <si>
-    <t>4. Click Owned again</t>
-  </si>
-  <si>
-    <t>The Owned column returns to the grid</t>
+    <t>Barcode matching ignores letter case</t>
+  </si>
+  <si>
+    <t>1. Search the barcode in its printed uppercase form, DFW0082529</t>
+  </si>
+  <si>
+    <t>2. Replace it with the same barcode in lowercase, dfw0082529, and search</t>
   </si>
   <si>
     <t>TC-ISR-PRS-018</t>
   </si>
   <si>
-    <t>An executed search survives leaving and returning</t>
-  </si>
-  <si>
-    <t>1. Type Amp into Any Field and click Search</t>
-  </si>
-  <si>
-    <t>Matching results load</t>
-  </si>
-  <si>
-    <t>2. note the count</t>
-  </si>
-  <si>
-    <t>The Any Field box still holds `Amp`, the same count shows, and the rows are back without clicking Search</t>
-  </si>
-  <si>
-    <t>3. Navigate away from the page entirely, then navigate back and wait for hydration</t>
+    <t>A shortened barcode matches nothing</t>
+  </si>
+  <si>
+    <t>1. Search the full barcode 5052320</t>
+  </si>
+  <si>
+    <t>One product found</t>
+  </si>
+  <si>
+    <t>2. Replace it with the first six digits, 505232, and search</t>
+  </si>
+  <si>
+    <t>Zero products found and the "No results" empty state</t>
+  </si>
+  <si>
+    <t>3. Search the full barcode again with a space typed in front of it</t>
+  </si>
+  <si>
+    <t>Zero products found</t>
   </si>
   <si>
     <t>TC-ISR-PRS-019</t>
   </si>
   <si>
-    <t>The search panel collapses and expands</t>
-  </si>
-  <si>
-    <t>1. Click the collapse-search-panel button</t>
-  </si>
-  <si>
-    <t>The search panel hides and the grid area widens</t>
-  </si>
-  <si>
-    <t>2. Click the button again</t>
-  </si>
-  <si>
-    <t>The search panel returns with its values intact</t>
+    <t>The barcode box and the Any Field box clear each other</t>
+  </si>
+  <si>
+    <t>The Products page is open with default criteria</t>
+  </si>
+  <si>
+    <t>1. Type a word into the Any Field box</t>
+  </si>
+  <si>
+    <t>The word is held; the barcode box is empty</t>
+  </si>
+  <si>
+    <t>2. Type a barcode into the barcode box</t>
+  </si>
+  <si>
+    <t>The barcode is held and the Any Field box has emptied</t>
+  </si>
+  <si>
+    <t>3. Type a word into the Any Field box again</t>
+  </si>
+  <si>
+    <t>The word is held and the barcode box has emptied</t>
+  </si>
+  <si>
+    <t>4. Click Reset</t>
+  </si>
+  <si>
+    <t>Both boxes are empty</t>
+  </si>
+  <si>
+    <t>TC-ISR-PRS-020</t>
+  </si>
+  <si>
+    <t>A barcode search survives leaving and returning</t>
+  </si>
+  <si>
+    <t>1. Search the barcode 1013104</t>
+  </si>
+  <si>
+    <t>One product found, a single row</t>
+  </si>
+  <si>
+    <t>2. Navigate away to Product Groups and back to Products</t>
+  </si>
+  <si>
+    <t>The page returns with the barcode still in its box</t>
+  </si>
+  <si>
+    <t>3. Read the count and the row without searching again</t>
+  </si>
+  <si>
+    <t>One product found, and the row is the same product as before</t>
+  </si>
+  <si>
+    <t>TC-ISR-PRS-021</t>
+  </si>
+  <si>
+    <t>A product found by barcode opens in the product-code dialog</t>
+  </si>
+  <si>
+    <t>1. Search the barcode 5052320</t>
+  </si>
+  <si>
+    <t>One row, Product Code ID 28592</t>
+  </si>
+  <si>
+    <t>2. Select that row</t>
+  </si>
+  <si>
+    <t>The row-selection toolbar appears</t>
+  </si>
+  <si>
+    <t>3. Click View Product Code</t>
+  </si>
+  <si>
+    <t>The details dialog opens on the Item tab and shows the same product</t>
   </si>
   <si>
     <t>TC-ISR-PRS-022</t>
-  </si>
-  <si>
-    <t>A numeric barcode returns the single product it is scanned under</t>
-  </si>
-  <si>
-    <t>The Products page is open with default criteria and no executed search</t>
-  </si>
-  <si>
-    <t>1. Type the barcode 5052320 into the barcode box</t>
-  </si>
-  <si>
-    <t>The box holds the value; the Any Field box stays empty</t>
-  </si>
-  <si>
-    <t>2. Click Search</t>
-  </si>
-  <si>
-    <t>The count reads one product found and the grid shows a single row</t>
-  </si>
-  <si>
-    <t>3. Read that row's Item and Product Code ID</t>
-  </si>
-  <si>
-    <t>Item "Allen &amp; Heath ZED24", Product Code ID 28592</t>
-  </si>
-  <si>
-    <t>TC-ISR-PRS-023</t>
-  </si>
-  <si>
-    <t>A barcode with letters resolves the same way as a numeric one</t>
-  </si>
-  <si>
-    <t>1. Type the barcode DFW0082529 into the barcode box</t>
-  </si>
-  <si>
-    <t>The box holds the value</t>
-  </si>
-  <si>
-    <t>One product found, a single row in the grid</t>
-  </si>
-  <si>
-    <t>Item "Shure ULXD1 Bodypack - G50", Product Code ID 71154</t>
-  </si>
-  <si>
-    <t>TC-ISR-PRS-024</t>
-  </si>
-  <si>
-    <t>Different barcodes on the same product all return that product</t>
-  </si>
-  <si>
-    <t>1. Search the barcode DFW0082529 and read the row's Product Code ID</t>
-  </si>
-  <si>
-    <t>One row, Product Code ID 71154</t>
-  </si>
-  <si>
-    <t>2. Replace the barcode with DFW0082517 and search again</t>
-  </si>
-  <si>
-    <t>One row, the same Product Code ID 71154</t>
-  </si>
-  <si>
-    <t>3. Replace the barcode with 5189939 and search again</t>
-  </si>
-  <si>
-    <t>TC-ISR-PRS-025</t>
-  </si>
-  <si>
-    <t>Barcode matching ignores letter case</t>
-  </si>
-  <si>
-    <t>1. Search the barcode in its printed uppercase form, DFW0082529</t>
-  </si>
-  <si>
-    <t>2. Replace it with the same barcode in lowercase, dfw0082529, and search</t>
-  </si>
-  <si>
-    <t>TC-ISR-PRS-026</t>
-  </si>
-  <si>
-    <t>A shortened barcode matches nothing</t>
-  </si>
-  <si>
-    <t>1. Search the full barcode 5052320</t>
-  </si>
-  <si>
-    <t>One product found</t>
-  </si>
-  <si>
-    <t>2. Replace it with the first six digits, 505232, and search</t>
-  </si>
-  <si>
-    <t>Zero products found and the "No results" empty state</t>
-  </si>
-  <si>
-    <t>3. Search the full barcode again with a space typed in front of it</t>
-  </si>
-  <si>
-    <t>Zero products found</t>
-  </si>
-  <si>
-    <t>TC-ISR-PRS-027</t>
-  </si>
-  <si>
-    <t>The barcode box and the Any Field box clear each other</t>
-  </si>
-  <si>
-    <t>The Products page is open with default criteria</t>
-  </si>
-  <si>
-    <t>1. Type a word into the Any Field box</t>
-  </si>
-  <si>
-    <t>The word is held; the barcode box is empty</t>
-  </si>
-  <si>
-    <t>2. Type a barcode into the barcode box</t>
-  </si>
-  <si>
-    <t>The barcode is held and the Any Field box has emptied</t>
-  </si>
-  <si>
-    <t>3. Type a word into the Any Field box again</t>
-  </si>
-  <si>
-    <t>The word is held and the barcode box has emptied</t>
-  </si>
-  <si>
-    <t>4. Click Reset</t>
-  </si>
-  <si>
-    <t>Both boxes are empty</t>
-  </si>
-  <si>
-    <t>TC-ISR-PRS-028</t>
-  </si>
-  <si>
-    <t>A barcode search survives leaving and returning</t>
-  </si>
-  <si>
-    <t>1. Search the barcode 1013104</t>
-  </si>
-  <si>
-    <t>One product found, a single row</t>
-  </si>
-  <si>
-    <t>2. Navigate away to Product Groups and back to Products</t>
-  </si>
-  <si>
-    <t>The page returns with the barcode still in its box</t>
-  </si>
-  <si>
-    <t>3. Read the count and the row without searching again</t>
-  </si>
-  <si>
-    <t>One product found, and the row is the same product as before</t>
-  </si>
-  <si>
-    <t>TC-ISR-PRS-029</t>
-  </si>
-  <si>
-    <t>A product found by barcode opens in the product-code dialog</t>
-  </si>
-  <si>
-    <t>1. Search the barcode 5052320</t>
-  </si>
-  <si>
-    <t>One row, Product Code ID 28592</t>
-  </si>
-  <si>
-    <t>2. Select that row</t>
-  </si>
-  <si>
-    <t>The row-selection toolbar appears</t>
-  </si>
-  <si>
-    <t>3. Click View Product Code</t>
-  </si>
-  <si>
-    <t>The details dialog opens on the Item tab and shows the same product</t>
-  </si>
-  <si>
-    <t>TC-ISR-PRS-030</t>
   </si>
   <si>
     <t>The barcode box stops accepting characters at its limit</t>
